--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487626_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487626_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5253</v>
+        <v>4.9313</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0414</v>
+        <v>6.202</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.516</v>
+        <v>-1.2708</v>
       </c>
       <c r="G2" t="n">
         <v>4.1893</v>
@@ -610,13 +610,13 @@
         <v>0.7761</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5763</v>
+        <v>0.9822</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1828</v>
+        <v>0.3435</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3935</v>
+        <v>0.6388</v>
       </c>
       <c r="V2" t="n">
         <v>-1.0164</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. MARTINEZ ALVAREZ</t>
+          <t>E. PASCUAL COZAR</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0444</v>
+        <v>3.2576</v>
       </c>
       <c r="E3" t="n">
-        <v>2.3022</v>
+        <v>3.949</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7422</v>
+        <v>-0.6914</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.09320000000000001</v>
+        <v>5.8465</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.9977</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0117</v>
+        <v>4.8488</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7095</v>
+        <v>5.8919</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7044</v>
+        <v>0.7538</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005</v>
+        <v>5.138</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8027</v>
+        <v>-0.0454</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.786</v>
+        <v>0.2439</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0167</v>
+        <v>-0.2892</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1642</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q3" t="n">
+        <v>-1.9403</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.3582</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.5633</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-0.0025</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.5659</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-2.5701</v>
+      </c>
+      <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>1.1642</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.5153</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.1346</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.3807</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.4582</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.4582</v>
-      </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-2.5701</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. PASCUAL COZAR</t>
+          <t>E. MARTINEZ ALVAREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7605</v>
+        <v>2.9626</v>
       </c>
       <c r="E4" t="n">
-        <v>3.5881</v>
+        <v>2.3022</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8277</v>
+        <v>0.6604</v>
       </c>
       <c r="G4" t="n">
-        <v>5.8465</v>
+        <v>-0.09320000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9977</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8488</v>
+        <v>-0.0117</v>
       </c>
       <c r="J4" t="n">
-        <v>5.8919</v>
+        <v>0.7095</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7538</v>
+        <v>0.7044</v>
       </c>
       <c r="L4" t="n">
-        <v>5.138</v>
+        <v>0.005</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0454</v>
+        <v>-0.8027</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2439</v>
+        <v>-0.786</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2892</v>
+        <v>-0.0167</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5821</v>
+        <v>1.1642</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3582</v>
+        <v>1.1642</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.4335</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3634</v>
+        <v>0.1346</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4296</v>
+        <v>0.2989</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.5701</v>
+        <v>1.4582</v>
       </c>
       <c r="W4" t="n">
+        <v>1.4582</v>
+      </c>
+      <c r="X4" t="n">
         <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>-2.5701</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0532</v>
+        <v>1.9502</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8429</v>
+        <v>1.9035</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2103</v>
+        <v>0.0468</v>
       </c>
       <c r="G5" t="n">
         <v>1.1574</v>
@@ -844,13 +844,13 @@
         <v>0.7761</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2122</v>
+        <v>1.1092</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1828</v>
+        <v>0.2434</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0294</v>
+        <v>0.8659</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1224</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. HERMOSO ALCUBILLA</t>
+          <t>J. OLIVA SANCHEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1343</v>
+        <v>1.2663</v>
       </c>
       <c r="E6" t="n">
-        <v>1.5196</v>
+        <v>1.9011</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3853</v>
+        <v>-0.6349</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.8846000000000001</v>
+        <v>2.7397</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4533</v>
+        <v>1.1097</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3379</v>
+        <v>1.63</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4333</v>
+        <v>3.8647</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3429</v>
+        <v>1.9567</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.7762</v>
+        <v>1.908</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.4513</v>
+        <v>-1.125</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1104</v>
+        <v>-0.8469</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5617</v>
+        <v>-0.2781</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5523</v>
+        <v>-0.9702</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5523</v>
+        <v>0.9702</v>
       </c>
       <c r="S6" t="n">
-        <v>1.201</v>
+        <v>-0.2212</v>
       </c>
       <c r="T6" t="n">
-        <v>0.729</v>
+        <v>-0.3054</v>
       </c>
       <c r="U6" t="n">
-        <v>0.472</v>
+        <v>0.08409999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7343</v>
+        <v>-0.2821</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2239</v>
+        <v>0.2821</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.9582</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. OLIVA SANCHEZ</t>
+          <t>M. KREISLER LORENTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.075</v>
+        <v>0.9159</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6008</v>
+        <v>0.4647</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5259</v>
+        <v>0.4512</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7397</v>
+        <v>-0.1477</v>
       </c>
       <c r="H7" t="n">
-        <v>1.1097</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>1.63</v>
+        <v>-0.7541</v>
       </c>
       <c r="J7" t="n">
-        <v>3.8647</v>
+        <v>0.7884</v>
       </c>
       <c r="K7" t="n">
-        <v>1.9567</v>
+        <v>1.3924</v>
       </c>
       <c r="L7" t="n">
-        <v>1.908</v>
+        <v>-0.6039</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.125</v>
+        <v>-0.9362</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8469</v>
+        <v>-0.786</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2781</v>
+        <v>-0.1502</v>
       </c>
       <c r="P7" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="Q7" t="n">
         <v>-0.9702</v>
       </c>
-      <c r="Q7" t="n">
-        <v>-1.9403</v>
-      </c>
       <c r="R7" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4125</v>
+        <v>0.2577</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6057</v>
+        <v>0.0345</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1932</v>
+        <v>0.2232</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2821</v>
+        <v>0.6119</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2821</v>
+        <v>0.6119</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. KREISLER LORENTE</t>
+          <t>M. HERMOSO ALCUBILLA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9615</v>
+        <v>0.9035</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5648</v>
+        <v>1.1798</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3967</v>
+        <v>-0.2763</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1477</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6064000000000001</v>
+        <v>1.4533</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.7541</v>
+        <v>-2.3379</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7884</v>
+        <v>-0.4333</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3924</v>
+        <v>1.3429</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6039</v>
+        <v>-1.7762</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9362</v>
+        <v>-0.4513</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.786</v>
+        <v>0.1104</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1502</v>
+        <v>-0.5617</v>
       </c>
       <c r="P8" t="n">
-        <v>0.194</v>
+        <v>1.5523</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3033</v>
+        <v>0.9702</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1346</v>
+        <v>0.3892</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1687</v>
+        <v>0.581</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6119</v>
+        <v>-0.7343</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6119</v>
+        <v>1.2239</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.9582</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0321</v>
+        <v>-0.068</v>
       </c>
       <c r="E9" t="n">
-        <v>1.647</v>
+        <v>1.5469</v>
       </c>
       <c r="F9" t="n">
         <v>-1.6148</v>
@@ -1156,10 +1156,10 @@
         <v>0.3881</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7638</v>
+        <v>0.6637</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1951</v>
+        <v>0.095</v>
       </c>
       <c r="U9" t="n">
         <v>0.5687</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0765</v>
+        <v>-2.2133</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3808</v>
+        <v>0.0805</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.4573</v>
+        <v>-2.2938</v>
       </c>
       <c r="G10" t="n">
         <v>0.0982</v>
@@ -1234,13 +1234,13 @@
         <v>0.5821</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8133</v>
+        <v>0.6766</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6808</v>
+        <v>0.3805</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1326</v>
+        <v>0.2961</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6597</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4383</v>
+        <v>-2.5319</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3738</v>
+        <v>-2.113</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0646</v>
+        <v>-0.4189</v>
       </c>
       <c r="G11" t="n">
         <v>-1.1245</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>1.6907</v>
+        <v>1.5971</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3163</v>
+        <v>0.577</v>
       </c>
       <c r="U11" t="n">
-        <v>1.3744</v>
+        <v>1.0201</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0642</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>11.0715</v>
+        <v>11.3742</v>
       </c>
       <c r="E12" t="n">
-        <v>17.1138</v>
+        <v>17.4167</v>
       </c>
       <c r="F12" t="n">
-        <v>-6.042400000000001</v>
+        <v>-6.0425</v>
       </c>
       <c r="G12" t="n">
         <v>12.5733</v>
@@ -1360,7 +1360,7 @@
         <v>7.1511</v>
       </c>
       <c r="I12" t="n">
-        <v>5.422199999999998</v>
+        <v>5.422199999999999</v>
       </c>
       <c r="J12" t="n">
         <v>22.5406</v>
@@ -1390,13 +1390,13 @@
         <v>9.701700000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>6.7296</v>
+        <v>7.032299999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>1.5869</v>
+        <v>1.8898</v>
       </c>
       <c r="U12" t="n">
-        <v>5.1428</v>
+        <v>5.1427</v>
       </c>
       <c r="V12" t="n">
         <v>-5.3209</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1867</v>
+        <v>2.5932</v>
       </c>
       <c r="E13" t="n">
-        <v>3.8339</v>
+        <v>4.1342</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6473</v>
+        <v>-1.5411</v>
       </c>
       <c r="G13" t="n">
         <v>-0.2312</v>
@@ -1468,13 +1468,13 @@
         <v>1.7463</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.6433</v>
+        <v>-1.2368</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.2596</v>
+        <v>-0.9593</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3838</v>
+        <v>-0.2776</v>
       </c>
       <c r="V13" t="n">
         <v>5.2253</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.4694</v>
+        <v>-0.2542</v>
       </c>
       <c r="E14" t="n">
         <v>0.5234</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9928</v>
+        <v>-0.7776</v>
       </c>
       <c r="G14" t="n">
         <v>-0.188</v>
@@ -1546,13 +1546,13 @@
         <v>0.194</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7575</v>
+        <v>-0.5423</v>
       </c>
       <c r="T14" t="n">
         <v>-0.4116</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.3459</v>
+        <v>-0.1307</v>
       </c>
       <c r="V14" t="n">
         <v>0.2821</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9455</v>
+        <v>-1.3765</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3621</v>
+        <v>1.6614</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.3076</v>
+        <v>-3.0379</v>
       </c>
       <c r="G15" t="n">
         <v>-1.5069</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5148</v>
+        <v>-0.9458</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1233</v>
+        <v>-0.5774</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6381</v>
+        <v>-0.3684</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2821</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.2163</v>
+        <v>-1.535</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.3698</v>
+        <v>-0.7702</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8465</v>
+        <v>-0.7648</v>
       </c>
       <c r="G16" t="n">
         <v>-2.4967</v>
@@ -1702,13 +1702,13 @@
         <v>1.1642</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1162</v>
+        <v>-0.2025</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1346</v>
+        <v>-0.2658</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0184</v>
+        <v>0.0634</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>F. REJON MIGUEL</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.7174</v>
+        <v>-1.7705</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6552</v>
+        <v>0.3104</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0622</v>
+        <v>-2.0809</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.659</v>
+        <v>-2.5353</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5750999999999999</v>
+        <v>-3.3828</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0839</v>
+        <v>0.8475</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0618</v>
+        <v>-0.1641</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.346</v>
+        <v>-2.2574</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2842</v>
+        <v>2.0933</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5971</v>
+        <v>-2.3712</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.229</v>
+        <v>-1.1254</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.3681</v>
+        <v>-1.2458</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3582</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3582</v>
+        <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5704</v>
+        <v>-0.5187</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5933</v>
+        <v>-0.5687</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0229</v>
+        <v>0.0499</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.8462</v>
+        <v>2.4477</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>3.9537</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.8462</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>F. REJON MIGUEL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8166</v>
+        <v>-1.8353</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09</v>
+        <v>-0.5551</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.7266</v>
+        <v>-1.2803</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5353</v>
+        <v>-1.659</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.3828</v>
+        <v>-0.5750999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8475</v>
+        <v>-1.0839</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1641</v>
+        <v>-0.0618</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.2574</v>
+        <v>-0.346</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0933</v>
+        <v>0.2842</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3712</v>
+        <v>-1.5971</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1254</v>
+        <v>-0.229</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.2458</v>
+        <v>-1.3681</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5648</v>
+        <v>-0.6884</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9691</v>
+        <v>-0.4932</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4043</v>
+        <v>-0.1951</v>
       </c>
       <c r="V18" t="n">
-        <v>2.4477</v>
+        <v>-0.8462</v>
       </c>
       <c r="W18" t="n">
-        <v>3.9537</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.506</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. GUEYE</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2776</v>
+        <v>-1.8638</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.8231000000000001</v>
+        <v>0.2246</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.4545</v>
+        <v>-2.0884</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.7574</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0297</v>
+        <v>-1.1328</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8459</v>
+        <v>0.3754</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8056</v>
+        <v>2.2313</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6838</v>
+        <v>-0.2018</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1218</v>
+        <v>2.4331</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6812</v>
+        <v>-2.9887</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7135</v>
+        <v>-0.931</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9677</v>
+        <v>-2.0577</v>
       </c>
       <c r="P19" t="n">
-        <v>0.194</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>2.5224</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0424</v>
+        <v>-0.7184</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0011</v>
+        <v>-0.9321</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0435</v>
+        <v>0.2137</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.5537</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.6597</v>
+        <v>1.8358</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.894</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3903</v>
+        <v>-2.0449</v>
       </c>
       <c r="E20" t="n">
-        <v>1.4368</v>
+        <v>1.5369</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8271</v>
+        <v>-3.5818</v>
       </c>
       <c r="G20" t="n">
         <v>-2.3234</v>
@@ -2014,13 +2014,13 @@
         <v>1.3582</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4729</v>
+        <v>-1.1275</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8356</v>
+        <v>-0.7355</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6373</v>
+        <v>-0.392</v>
       </c>
       <c r="V20" t="n">
         <v>0.0478</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>B. GUEYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4249</v>
+        <v>-2.3171</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1758</v>
+        <v>-1.0233</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2491</v>
+        <v>-1.2938</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7574</v>
+        <v>-0.8754999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1328</v>
+        <v>-0.0297</v>
       </c>
       <c r="I21" t="n">
-        <v>0.3754</v>
+        <v>-0.8459</v>
       </c>
       <c r="J21" t="n">
-        <v>2.2313</v>
+        <v>0.8056</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2018</v>
+        <v>0.6838</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4331</v>
+        <v>0.1218</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.9887</v>
+        <v>-1.6812</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.931</v>
+        <v>-0.7135</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0577</v>
+        <v>-0.9677</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>2.5224</v>
+        <v>1.1642</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.2795</v>
+        <v>-0.0819</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3325</v>
+        <v>-0.1991</v>
       </c>
       <c r="U21" t="n">
-        <v>0.053</v>
+        <v>0.1172</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.5537</v>
       </c>
       <c r="W21" t="n">
-        <v>1.8358</v>
+        <v>-0.6597</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.8358</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="22">
@@ -2125,28 +2125,28 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-11.0713</v>
+        <v>-10.4041</v>
       </c>
       <c r="E22" t="n">
-        <v>6.042299999999999</v>
+        <v>6.0423</v>
       </c>
       <c r="F22" t="n">
-        <v>-17.1137</v>
+        <v>-16.4466</v>
       </c>
       <c r="G22" t="n">
         <v>-12.5734</v>
       </c>
       <c r="H22" t="n">
-        <v>-7.151300000000001</v>
+        <v>-7.1513</v>
       </c>
       <c r="I22" t="n">
         <v>-5.422400000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>9.967400000000001</v>
+        <v>9.9674</v>
       </c>
       <c r="K22" t="n">
-        <v>1.6808</v>
+        <v>1.680799999999999</v>
       </c>
       <c r="L22" t="n">
         <v>8.2865</v>
@@ -2164,19 +2164,19 @@
         <v>2.9103</v>
       </c>
       <c r="Q22" t="n">
-        <v>-9.701699999999999</v>
+        <v>-9.701700000000001</v>
       </c>
       <c r="R22" t="n">
         <v>12.612</v>
       </c>
       <c r="S22" t="n">
-        <v>-6.7294</v>
+        <v>-6.0623</v>
       </c>
       <c r="T22" t="n">
         <v>-5.1427</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.5868</v>
+        <v>-0.9196</v>
       </c>
       <c r="V22" t="n">
         <v>5.3209</v>
